--- a/src/src/main/resources/tiefaces/tiefaces.xlsx
+++ b/src/src/main/resources/tiefaces/tiefaces.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18431"/>
-  <workbookPr filterPrivacy="1"/>
+  <workbookPr filterPrivacy="1" showInkAnnotation="0"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
@@ -44,7 +44,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-tie:form(name="sale report" length="9" headerLength="4" footerLength="1")</t>
+tie:form(name="sheet1" length="9" headerLength="4" footerLength="1")</t>
         </r>
       </text>
     </comment>
@@ -68,7 +68,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-tie:each(items="departments", var="department", length="8" allowAdd="true")</t>
+tie:each(items="templateElementList", var="element", length="8" allowAdd="true")</t>
         </r>
       </text>
     </comment>
@@ -136,7 +136,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>${department.name}</t>
+    <t>${element.textValue}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/src/src/main/resources/tiefaces/tiefaces.xlsx
+++ b/src/src/main/resources/tiefaces/tiefaces.xlsx
@@ -44,7 +44,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-tie:form(name="sheet1" length="9" headerLength="4" footerLength="1")</t>
+tie:form(name="sheet1" length="10" headerLength="1" footerLength="1")</t>
         </r>
       </text>
     </comment>
@@ -68,11 +68,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-tie:each(items="templateElementList", var="element", length="8" allowAdd="true")</t>
+tie:each(items="templateElementList", var="element", length="1" allowAdd="true")</t>
         </r>
       </text>
     </comment>
-    <comment ref="B2" authorId="0" shapeId="0">
+    <comment ref="D2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -92,8 +92,136 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-$widget.dropdown{itemLabels="Male;Female" itemValues="M;F" }
-</t>
+$widget.inputnumber{minValue="0" maxValue="9999" decimalPlaces="0"}</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+$widget.inputnumber{minValue="0" maxValue="9999" decimalPlaces="0"}</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+$widget.dropdown{itemLabels="</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>正常</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>;</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>加粗</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>;</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>斜体</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>" itemValues="0;1;2" }</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+$widget.dropdown{itemLabels="TimesRoman;Courier;Arial;Microsoft YaHei;SimHei;SimSun" itemValues="TimesRoman;Courier;Arial;Microsoft YaHei;SimHei;SimSun" }</t>
         </r>
       </text>
     </comment>
@@ -102,7 +230,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>文本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -137,6 +265,34 @@
   </si>
   <si>
     <t>${element.textValue}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${element.fieldKey}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${element.positionX}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${element.positionY}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${element.fontSize}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${element.fontType}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${element.fontName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>${element.colorStr}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -144,7 +300,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,6 +328,13 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -193,8 +356,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,119 +641,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.375" customWidth="1"/>
+    <col min="5" max="5" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="I2" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/src/src/main/resources/tiefaces/tiefaces.xlsx
+++ b/src/src/main/resources/tiefaces/tiefaces.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$2</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -72,6 +75,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+$widget.inputnumber{minValue="0" maxValue="9999" decimalPlaces="0"}</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
         <r>
@@ -96,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E2" authorId="0" shapeId="0">
+    <comment ref="F2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -116,7 +143,64 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-$widget.inputnumber{minValue="0" maxValue="9999" decimalPlaces="0"}</t>
+$widget.dropdown{itemLabels="</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>正常</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>;</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>加粗</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>;</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>斜体</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>" itemValues="0;1;2" }</t>
         </r>
       </text>
     </comment>
@@ -140,64 +224,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-$widget.dropdown{itemLabels="</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>正常</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>;</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>加粗</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>;</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>斜体</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>" itemValues="0;1;2" }</t>
+$widget.dropdown{itemLabels="TimesRoman;Courier;Arial;Microsoft YaHei;SimHei;SimSun" itemValues="TimesRoman;Courier;Arial;Microsoft YaHei;SimHei;SimSun" }</t>
         </r>
       </text>
     </comment>
@@ -221,7 +248,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-$widget.dropdown{itemLabels="TimesRoman;Courier;Arial;Microsoft YaHei;SimHei;SimSun" itemValues="TimesRoman;Courier;Arial;Microsoft YaHei;SimHei;SimSun" }</t>
+$widget.inputnumber{}</t>
         </r>
       </text>
     </comment>
@@ -641,69 +668,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.375" customWidth="1"/>
-    <col min="5" max="5" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" customWidth="1"/>
+    <col min="4" max="4" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H2"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
